--- a/public/xlsx/sample.xlsx
+++ b/public/xlsx/sample.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="18">
   <si>
     <t xml:space="preserve">id</t>
   </si>
@@ -62,6 +62,18 @@
   </si>
   <si>
     <t xml:space="preserve">ceo@gofsolution.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DDD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">yyy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">prod</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gofcon77@gmail.com</t>
   </si>
 </sst>
 </file>
@@ -293,7 +305,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="16.42"/>
@@ -363,6 +375,23 @@
       </c>
       <c r="E4" s="4" t="s">
         <v>13</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" s="0" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" s="0" t="s">
+        <v>15</v>
+      </c>
+      <c r="D5" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -374,6 +403,7 @@
     <hyperlink ref="E2" r:id="rId1" display="arazorback77@gmail.com"/>
     <hyperlink ref="E3" r:id="rId2" display="javanance@gmail.com"/>
     <hyperlink ref="E4" r:id="rId3" display="ceo@gofsolution.com"/>
+    <hyperlink ref="E5" r:id="rId4" display="gofcon77@gmail.com"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
